--- a/program/산출물양식/[모델배포]_요구사항 정의서_A-COPilot.xlsx
+++ b/program/산출물양식/[모델배포]_요구사항 정의서_A-COPilot.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="F30" s="51" t="inlineStr">
         <is>
-          <t>MCP는 외부 AI가 우리 기능을 도구로 불러 쓰게 하는 규약이다. 쓰기는 3단계 경계를 둔다.</t>
+          <t>지금 여는 것은 제한된 검증 범위의 문의와 조회다. 전면 Commerce Ops는 확장 범위다.</t>
         </is>
       </c>
       <c r="G30" s="51" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="F35" s="47" t="inlineStr">
         <is>
-          <t>검증용 쇼핑몰 연계 범위다. 일정에 따라 배치가 조정될 수 있다.</t>
+          <t>확장 범위다. 검증 쇼핑몰이 준비되는 대로 진행한다. 이번 기간 착수 범위가 아니다.</t>
         </is>
       </c>
       <c r="G35" s="47" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>확장 범위</t>
         </is>
       </c>
       <c r="H35" s="2" t="n"/>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G36" s="54" t="inlineStr">
         <is>
-          <t>미착수 범위</t>
+          <t>확장 범위</t>
         </is>
       </c>
       <c r="H36" s="2" t="n"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G39" s="47" t="inlineStr">
         <is>
-          <t>구현됨 (v2 apply와 병행)</t>
+          <t>구현됨. v2 apply와 병행</t>
         </is>
       </c>
       <c r="H39" s="2" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="G40" s="54" t="inlineStr">
         <is>
-          <t>★미구현 — 계약 확정 단계</t>
+          <t>미구현. 계약 확정 단계</t>
         </is>
       </c>
       <c r="H40" s="2" t="n"/>
